--- a/xls/revisao_probabilidade.xlsx
+++ b/xls/revisao_probabilidade.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\OneDrive\Documentos\estatistica2024\xls\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_0744248A96CE579F7469644CC809FDF631B92862" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2274EE75-583B-4B99-8601-228E94F81529}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="105" windowWidth="12375" windowHeight="8925"/>
+    <workbookView xWindow="675" yWindow="2085" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="exemplo1" sheetId="1" r:id="rId1"/>
@@ -19,17 +20,30 @@
     <definedName name="mc_dependents" localSheetId="1">exemplo2!$K$13</definedName>
     <definedName name="mc_output" localSheetId="1">exemplo2!$P$1</definedName>
   </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>camilo</author>
   </authors>
   <commentList>
-    <comment ref="K13" authorId="0" shapeId="0">
+    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
       <text>
         <r>
           <rPr>
@@ -37,7 +51,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>camilo:</t>
         </r>
@@ -46,7 +60,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 (1 = mesma cor; 0 = cores diferentes)</t>
@@ -58,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
   <si>
     <t>Valores</t>
   </si>
@@ -109,12 +123,21 @@
   </si>
   <si>
     <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2024</t>
+  </si>
+  <si>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
+  </si>
+  <si>
+    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
+  </si>
+  <si>
+    <t>#https://cdrenno.github.io/Estatistica/</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -131,14 +154,14 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="12"/>
@@ -189,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -202,7 +225,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -243,7 +265,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="pt-BR"/>
   <c:roundedCorners val="0"/>
@@ -272,7 +294,6 @@
           </a:p>
         </c:rich>
       </c:tx>
-      <c:layout/>
       <c:overlay val="0"/>
     </c:title>
     <c:autoTitleDeleted val="0"/>
@@ -319,26 +340,31 @@
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>0.1</c:v>
                 </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.3</c:v>
-                </c:pt>
-                <c:pt idx="2">
+                <c:pt idx="3">
                   <c:v>0.2</c:v>
                 </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.4</c:v>
-                </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-5214-4F8A-A281-D63C2D03BDC8}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -375,7 +401,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
@@ -433,7 +458,6 @@
               </a:p>
             </c:rich>
           </c:tx>
-          <c:layout/>
           <c:overlay val="0"/>
         </c:title>
         <c:numFmt formatCode="0.0" sourceLinked="0"/>
@@ -475,7 +499,13 @@
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="2064" name="Gráfico 1"/>
+        <xdr:cNvPr id="2064" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000010080000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -508,11 +538,17 @@
       <xdr:col>11</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="1046" name="Imagem 5"/>
+        <xdr:cNvPr id="1046" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0100-000016040000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -569,9 +605,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -609,9 +645,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -646,7 +682,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -681,7 +717,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -854,7 +890,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="21"/>
   <cols>
@@ -879,115 +915,115 @@
     <row r="2" spans="1:6">
       <c r="A2" s="5">
         <f ca="1">RANDBETWEEN(1,6)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C2" s="5">
         <v>1</v>
       </c>
       <c r="D2" s="2">
         <f t="shared" ref="D2:D7" ca="1" si="0">COUNTIF(A:A,C2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="4">
         <f t="shared" ref="E2:E7" ca="1" si="1">D2/D$8</f>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="3"/>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A11" ca="1" si="2">RANDBETWEEN(1,6)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
       </c>
       <c r="D3" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5">
         <v>3</v>
       </c>
       <c r="D4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C5" s="5">
         <v>4</v>
       </c>
       <c r="D5" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5">
         <v>5</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C7" s="5">
         <v>6</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>2</v>
@@ -1016,7 +1052,7 @@
     <row r="11" spans="1:6">
       <c r="A11" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="7:7">
@@ -1037,35 +1073,40 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:T22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="2:20" ht="15.75">
+    <row r="1" spans="2:20">
       <c r="O1" s="7" t="s">
         <v>10</v>
       </c>
       <c r="R1" t="s">
         <v>13</v>
       </c>
-      <c r="T1" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="2:20" ht="15.75">
+      <c r="T1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="2:20">
       <c r="O2" s="7" t="s">
         <v>12</v>
       </c>
       <c r="P2">
         <f ca="1">SUM(K:K)/COUNT(K:K)</f>
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="R2">
         <f>13/60</f>
         <v>0.21666666666666667</v>
       </c>
-      <c r="T2" s="2" t="s">
-        <v>15</v>
+      <c r="T2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="2:20">
+      <c r="T3" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="2:20">
@@ -1079,7 +1120,7 @@
       </c>
       <c r="P5">
         <f ca="1">SUM(O:O)/COUNT(O:O)</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R5">
         <f>28/75</f>
@@ -1108,10 +1149,9 @@
         <v>5</v>
       </c>
       <c r="E13" s="6"/>
-      <c r="F13" s="8"/>
       <c r="G13" s="6" t="str">
         <f ca="1">CHOOSE(RANDBETWEEN(1,6),$B$13,$B$14,$B$15,$B$16,$B$17,$B$18)</f>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="H13">
         <f ca="1">RANDBETWEEN(1,5)</f>
@@ -1123,11 +1163,11 @@
       </c>
       <c r="J13" t="str">
         <f ca="1">CHOOSE(MOD(H13+RANDBETWEEN(1,4)-1,5)+1,G$13,E$14,E$15,E$16,E$17,G$13)</f>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="K13">
         <f ca="1">IF(I13=J13,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="str">
         <f ca="1">CHOOSE(RANDBETWEEN(1,5),G$13,E$14,E$15,E$16,E$17)</f>
@@ -1135,7 +1175,7 @@
       </c>
       <c r="N13" t="str">
         <f ca="1">CHOOSE(RANDBETWEEN(1,5),G$13,E$14,E$15,E$16,E$17)</f>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="O13">
         <f ca="1">IF(M13=N13,1,0)</f>
@@ -1155,7 +1195,7 @@
       </c>
       <c r="H14">
         <f t="shared" ref="H14:H22" ca="1" si="1">RANDBETWEEN(1,5)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="str">
         <f t="shared" ref="I14:I22" ca="1" si="2">CHOOSE(H14,G$13,E$14,E$15,E$16,E$17)</f>
@@ -1163,15 +1203,15 @@
       </c>
       <c r="J14" t="str">
         <f t="shared" ref="J14:J22" ca="1" si="3">CHOOSE(MOD(H14+RANDBETWEEN(1,4)-1,5)+1,G$13,E$14,E$15,E$16,E$17,G$13)</f>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="K14">
         <f t="shared" ref="K14:K22" ca="1" si="4">IF(I14=J14,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="str">
         <f t="shared" ref="M14:M22" ca="1" si="5">CHOOSE(RANDBETWEEN(1,5),G$13,E$14,E$15,E$16,E$17)</f>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" ref="N14:N22" ca="1" si="6">CHOOSE(RANDBETWEEN(1,5),G$13,E$14,E$15,E$16,E$17)</f>
@@ -1179,7 +1219,7 @@
       </c>
       <c r="O14">
         <f t="shared" ref="O14:O22" ca="1" si="7">IF(M14=N14,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="2:20" ht="15.75" thickBot="1">
@@ -1195,7 +1235,7 @@
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1211,7 +1251,7 @@
       </c>
       <c r="M15" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -1219,7 +1259,7 @@
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="2:20" ht="15.75" thickBot="1">
@@ -1231,35 +1271,35 @@
       </c>
       <c r="G16" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>R</v>
+        <v>B</v>
       </c>
       <c r="H16">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>B</v>
+        <v>G</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="2:15" ht="15.75" thickBot="1">
@@ -1271,19 +1311,19 @@
       </c>
       <c r="G17" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="H17">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I17" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>G</v>
+        <v>B</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="K17">
         <f t="shared" ca="1" si="4"/>
@@ -1308,19 +1348,19 @@
       </c>
       <c r="G18" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="H18">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I18" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>G</v>
+        <v>B</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="4"/>
@@ -1328,11 +1368,11 @@
       </c>
       <c r="M18" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>R</v>
+        <v>B</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="7"/>
@@ -1342,19 +1382,19 @@
     <row r="19" spans="2:15" ht="15.75" thickBot="1">
       <c r="G19" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="H19">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="4"/>
@@ -1362,7 +1402,7 @@
       </c>
       <c r="M19" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -1370,17 +1410,17 @@
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="15.75" thickBot="1">
       <c r="G20" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="H20">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I20" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1388,23 +1428,23 @@
       </c>
       <c r="J20" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M20" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>B</v>
+        <v>G</v>
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="15.75" thickBot="1">
@@ -1414,11 +1454,11 @@
       </c>
       <c r="H21">
         <f t="shared" ca="1" si="1"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I21" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>G</v>
+        <v>B</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1426,7 +1466,7 @@
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -1434,11 +1474,11 @@
       </c>
       <c r="N21" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>B</v>
+        <v>G</v>
       </c>
       <c r="O21">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="15.75" thickBot="1">
@@ -1448,15 +1488,15 @@
       </c>
       <c r="H22">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I22" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="K22">
         <f t="shared" ca="1" si="4"/>
@@ -1468,15 +1508,15 @@
       </c>
       <c r="N22" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="O22">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B13:B18 E13:F17 I13:J506 M13:N506 G13:G22">
+  <conditionalFormatting sqref="E13:F17 B13:B18 G13:G22 I13:J506 M13:N506">
     <cfRule type="cellIs" dxfId="2" priority="34" stopIfTrue="1" operator="equal">
       <formula>"B"</formula>
     </cfRule>

--- a/xls/revisao_probabilidade.xlsx
+++ b/xls/revisao_probabilidade.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2025/xls/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/eac9aab033b2f962/Documentos/estatistica2026/xls/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_0744248A96CE579F7469644CC809FDF631B92862" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2274EE75-583B-4B99-8601-228E94F81529}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_0744248A96CE579F7469644CC809FDF631B92862" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AE706BD2-B28B-4FE1-B807-1F554293D00B}"/>
   <bookViews>
-    <workbookView xWindow="675" yWindow="2085" windowWidth="26610" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="exemplo1" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="17">
   <si>
     <t>Valores</t>
   </si>
@@ -119,19 +119,10 @@
     <t>Bola Urna A</t>
   </si>
   <si>
-    <t>#http://www.dpi.inpe.br/~camilo/estatistica</t>
-  </si>
-  <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2024</t>
-  </si>
-  <si>
-    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2025</t>
-  </si>
-  <si>
-    <t>#http://urlib.net/8JMKD2USNRW34T/4D6DMD2</t>
-  </si>
-  <si>
     <t>#https://cdrenno.github.io/Estatistica/</t>
+  </si>
+  <si>
+    <t>#Estatística: Aplicação ao Sensoriamento Remoto - SER204, INPE, 2026</t>
   </si>
 </sst>
 </file>
@@ -346,16 +337,16 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0.1</c:v>
+                  <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>0.2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.5</c:v>
+                  <c:v>0.1</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>0.2</c:v>
+                  <c:v>0.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -891,7 +882,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="21"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="5"/>
@@ -933,7 +924,7 @@
     <row r="3" spans="1:6">
       <c r="A3" s="5">
         <f t="shared" ref="A3:A11" ca="1" si="2">RANDBETWEEN(1,6)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C3" s="5">
         <v>2</v>
@@ -958,18 +949,18 @@
       </c>
       <c r="D4" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="5">
         <v>4</v>
@@ -987,43 +978,43 @@
     <row r="6" spans="1:6">
       <c r="A6" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C6" s="5">
         <v>5</v>
       </c>
       <c r="D6" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="F6" s="3"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C7" s="5">
         <v>6</v>
       </c>
       <c r="D7" s="2">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4">
         <f t="shared" ca="1" si="1"/>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>2</v>
@@ -1040,30 +1031,33 @@
     <row r="9" spans="1:6">
       <c r="A9" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="5">
         <f t="shared" ca="1" si="2"/>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="7:7">
-      <c r="G17" s="2" t="s">
+      <c r="G17" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="18" spans="7:7">
-      <c r="G18" s="2" t="s">
+      <c r="G18" t="s">
         <v>15</v>
       </c>
+    </row>
+    <row r="19" spans="7:7">
+      <c r="G19"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1085,7 +1079,7 @@
         <v>13</v>
       </c>
       <c r="T1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="2:20">
@@ -1094,19 +1088,14 @@
       </c>
       <c r="P2">
         <f ca="1">SUM(K:K)/COUNT(K:K)</f>
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="R2">
         <f>13/60</f>
         <v>0.21666666666666667</v>
       </c>
       <c r="T2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="2:20">
-      <c r="T3" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="2:20">
@@ -1120,7 +1109,7 @@
       </c>
       <c r="P5">
         <f ca="1">SUM(O:O)/COUNT(O:O)</f>
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="R5">
         <f>28/75</f>
@@ -1155,11 +1144,11 @@
       </c>
       <c r="H13">
         <f ca="1">RANDBETWEEN(1,5)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I13" t="str">
         <f ca="1">CHOOSE(H13,G$13,E$14,E$15,E$16,E$17)</f>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="J13" t="str">
         <f ca="1">CHOOSE(MOD(H13+RANDBETWEEN(1,4)-1,5)+1,G$13,E$14,E$15,E$16,E$17,G$13)</f>
@@ -1167,11 +1156,11 @@
       </c>
       <c r="K13">
         <f ca="1">IF(I13=J13,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="str">
         <f ca="1">CHOOSE(RANDBETWEEN(1,5),G$13,E$14,E$15,E$16,E$17)</f>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="N13" t="str">
         <f ca="1">CHOOSE(RANDBETWEEN(1,5),G$13,E$14,E$15,E$16,E$17)</f>
@@ -1179,7 +1168,7 @@
       </c>
       <c r="O13">
         <f ca="1">IF(M13=N13,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="2:20" ht="15.75" thickBot="1">
@@ -1203,19 +1192,19 @@
       </c>
       <c r="J14" t="str">
         <f t="shared" ref="J14:J22" ca="1" si="3">CHOOSE(MOD(H14+RANDBETWEEN(1,4)-1,5)+1,G$13,E$14,E$15,E$16,E$17,G$13)</f>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="K14">
         <f t="shared" ref="K14:K22" ca="1" si="4">IF(I14=J14,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="str">
         <f t="shared" ref="M14:M22" ca="1" si="5">CHOOSE(RANDBETWEEN(1,5),G$13,E$14,E$15,E$16,E$17)</f>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" ref="N14:N22" ca="1" si="6">CHOOSE(RANDBETWEEN(1,5),G$13,E$14,E$15,E$16,E$17)</f>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="O14">
         <f t="shared" ref="O14:O22" ca="1" si="7">IF(M14=N14,1,0)</f>
@@ -1231,19 +1220,19 @@
       </c>
       <c r="G15" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="H15">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="K15">
         <f t="shared" ca="1" si="4"/>
@@ -1251,11 +1240,11 @@
       </c>
       <c r="M15" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="O15">
         <f t="shared" ca="1" si="7"/>
@@ -1271,15 +1260,15 @@
       </c>
       <c r="G16" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="H16">
         <f t="shared" ca="1" si="1"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I16" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>R</v>
+        <v>B</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1287,7 +1276,7 @@
       </c>
       <c r="K16">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="str">
         <f t="shared" ca="1" si="5"/>
@@ -1295,11 +1284,11 @@
       </c>
       <c r="N16" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="O16">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:15" ht="15.75" thickBot="1">
@@ -1311,15 +1300,15 @@
       </c>
       <c r="G17" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>R</v>
+        <v>B</v>
       </c>
       <c r="H17">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I17" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>B</v>
+        <v>G</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1331,15 +1320,15 @@
       </c>
       <c r="M17" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="O17">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="2:15" ht="15.75" thickBot="1">
@@ -1348,11 +1337,11 @@
       </c>
       <c r="G18" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="H18">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I18" t="str">
         <f t="shared" ca="1" si="2"/>
@@ -1360,7 +1349,7 @@
       </c>
       <c r="J18" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>B</v>
+        <v>G</v>
       </c>
       <c r="K18">
         <f t="shared" ca="1" si="4"/>
@@ -1368,11 +1357,11 @@
       </c>
       <c r="M18" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="O18">
         <f t="shared" ca="1" si="7"/>
@@ -1382,19 +1371,19 @@
     <row r="19" spans="2:15" ht="15.75" thickBot="1">
       <c r="G19" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>G</v>
+        <v>B</v>
       </c>
       <c r="H19">
         <f t="shared" ca="1" si="1"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>R</v>
+        <v>G</v>
       </c>
       <c r="K19">
         <f t="shared" ca="1" si="4"/>
@@ -1406,25 +1395,25 @@
       </c>
       <c r="N19" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>G</v>
+        <v>B</v>
       </c>
       <c r="O19">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:15" ht="15.75" thickBot="1">
       <c r="G20" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="H20">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I20" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>G</v>
+        <v>B</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1432,11 +1421,11 @@
       </c>
       <c r="K20">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M20" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" ca="1" si="6"/>
@@ -1444,25 +1433,25 @@
       </c>
       <c r="O20">
         <f t="shared" ca="1" si="7"/>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="2:15" ht="15.75" thickBot="1">
       <c r="G21" s="6" t="str">
         <f t="shared" ca="1" si="0"/>
-        <v>R</v>
+        <v>B</v>
       </c>
       <c r="H21">
         <f t="shared" ca="1" si="1"/>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I21" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>B</v>
+        <v>G</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" ca="1" si="3"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="K21">
         <f t="shared" ca="1" si="4"/>
@@ -1470,15 +1459,15 @@
       </c>
       <c r="M21" t="str">
         <f t="shared" ca="1" si="5"/>
-        <v>B</v>
+        <v>R</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" ca="1" si="6"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="O21">
         <f t="shared" ca="1" si="7"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="2:15" ht="15.75" thickBot="1">
@@ -1488,11 +1477,11 @@
       </c>
       <c r="H22">
         <f t="shared" ca="1" si="1"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I22" t="str">
         <f t="shared" ca="1" si="2"/>
-        <v>G</v>
+        <v>R</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" ca="1" si="3"/>
@@ -1500,7 +1489,7 @@
       </c>
       <c r="K22">
         <f t="shared" ca="1" si="4"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M22" t="str">
         <f t="shared" ca="1" si="5"/>
